--- a/jogos_2025-05-06.xlsx
+++ b/jogos_2025-05-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="204">
   <si>
     <t>Date</t>
   </si>
@@ -127,60 +127,6 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
@@ -301,39 +247,39 @@
     <t>Kataller Toyama</t>
   </si>
   <si>
+    <t>Nagoya Grampus</t>
+  </si>
+  <si>
+    <t>Montedio Yamagata</t>
+  </si>
+  <si>
+    <t>Consadole Sapporo</t>
+  </si>
+  <si>
+    <t>Vissel Kobe</t>
+  </si>
+  <si>
+    <t>Avispa Fukuoka</t>
+  </si>
+  <si>
+    <t>Jeonbuk Motors</t>
+  </si>
+  <si>
     <t>Urawa Reds</t>
   </si>
   <si>
-    <t>Consadole Sapporo</t>
-  </si>
-  <si>
     <t>Renofa Yamaguchi</t>
   </si>
   <si>
-    <t>Avispa Fukuoka</t>
-  </si>
-  <si>
-    <t>Nagoya Grampus</t>
-  </si>
-  <si>
-    <t>Montedio Yamagata</t>
-  </si>
-  <si>
-    <t>Vissel Kobe</t>
-  </si>
-  <si>
-    <t>Jeonbuk Motors</t>
+    <t>Roasso Kumamoto</t>
+  </si>
+  <si>
+    <t>Ehime</t>
   </si>
   <si>
     <t>Blaublitz Akita</t>
   </si>
   <si>
-    <t>Ehime</t>
-  </si>
-  <si>
-    <t>Roasso Kumamoto</t>
-  </si>
-  <si>
     <t>Tokushima Vortis</t>
   </si>
   <si>
@@ -376,30 +322,30 @@
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Masr</t>
+  </si>
+  <si>
     <t>Yverdon Sport</t>
   </si>
   <si>
     <t>Västerås SK</t>
   </si>
   <si>
-    <t>Masr</t>
-  </si>
-  <si>
     <t>Golden Arrows</t>
   </si>
   <si>
     <t>Inter Milan</t>
   </si>
   <si>
+    <t>Carabobo</t>
+  </si>
+  <si>
+    <t>Atlético Bucaramanga</t>
+  </si>
+  <si>
     <t>Alianza Lima</t>
   </si>
   <si>
-    <t>Carabobo</t>
-  </si>
-  <si>
-    <t>Atlético Bucaramanga</t>
-  </si>
-  <si>
     <t>CRB</t>
   </si>
   <si>
@@ -418,39 +364,39 @@
     <t>V-Varen Nagasaki</t>
   </si>
   <si>
+    <t>Fagiano Okayama</t>
+  </si>
+  <si>
+    <t>Oita Trinita</t>
+  </si>
+  <si>
+    <t>Jubilo Iwata</t>
+  </si>
+  <si>
+    <t>Cerezo Osaka</t>
+  </si>
+  <si>
+    <t>Kashima Antlers</t>
+  </si>
+  <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
     <t>Gamba Osaka</t>
   </si>
   <si>
-    <t>Jubilo Iwata</t>
-  </si>
-  <si>
     <t>Mito Hollyhock</t>
   </si>
   <si>
-    <t>Kashima Antlers</t>
-  </si>
-  <si>
-    <t>Fagiano Okayama</t>
-  </si>
-  <si>
-    <t>Oita Trinita</t>
-  </si>
-  <si>
-    <t>Cerezo Osaka</t>
-  </si>
-  <si>
-    <t>Daejeon Citizen</t>
+    <t>Imabari</t>
+  </si>
+  <si>
+    <t>Iwaki</t>
   </si>
   <si>
     <t>Ventforet Kofu</t>
   </si>
   <si>
-    <t>Iwaki</t>
-  </si>
-  <si>
-    <t>Imabari</t>
-  </si>
-  <si>
     <t>Sagan Tosu</t>
   </si>
   <si>
@@ -493,30 +439,30 @@
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
     <t>St. Gallen</t>
   </si>
   <si>
     <t>Kalmar</t>
   </si>
   <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
     <t>Orlando Pirates</t>
   </si>
   <si>
     <t>FC Barcelona</t>
   </si>
   <si>
+    <t>Botafogo</t>
+  </si>
+  <si>
+    <t>Racing Club</t>
+  </si>
+  <si>
     <t>São Paulo</t>
   </si>
   <si>
-    <t>Botafogo</t>
-  </si>
-  <si>
-    <t>Racing Club</t>
-  </si>
-  <si>
     <t>Cuiabá</t>
   </si>
   <si>
@@ -541,21 +487,21 @@
     <t>[]</t>
   </si>
   <si>
+    <t>['25', '69', '90+4']</t>
+  </si>
+  <si>
     <t>['77', '81']</t>
   </si>
   <si>
+    <t>['45']</t>
+  </si>
+  <si>
+    <t>['88']</t>
+  </si>
+  <si>
     <t>['90+3']</t>
   </si>
   <si>
-    <t>['25', '69', '90+4']</t>
-  </si>
-  <si>
-    <t>['45']</t>
-  </si>
-  <si>
-    <t>['88']</t>
-  </si>
-  <si>
     <t>['27']</t>
   </si>
   <si>
@@ -607,27 +553,27 @@
     <t>['46', '55']</t>
   </si>
   <si>
+    <t>['1', '20', '25', '70']</t>
+  </si>
+  <si>
+    <t>['45+2', '83', '90+6']</t>
+  </si>
+  <si>
+    <t>['43']</t>
+  </si>
+  <si>
     <t>['53']</t>
   </si>
   <si>
-    <t>['1', '20', '25', '70']</t>
-  </si>
-  <si>
     <t>['38', '45']</t>
   </si>
   <si>
-    <t>['43']</t>
-  </si>
-  <si>
-    <t>['45+2', '83', '90+6']</t>
+    <t>['36']</t>
   </si>
   <si>
     <t>['48']</t>
   </si>
   <si>
-    <t>['36']</t>
-  </si>
-  <si>
     <t>['20']</t>
   </si>
   <si>
@@ -667,13 +613,13 @@
     <t>['54', '60', '87']</t>
   </si>
   <si>
+    <t>['22', '90+1']</t>
+  </si>
+  <si>
+    <t>['4', '56', '69', '90+4']</t>
+  </si>
+  <si>
     <t>['35', '89']</t>
-  </si>
-  <si>
-    <t>['22', '90+1']</t>
-  </si>
-  <si>
-    <t>['4', '56', '69', '90+4']</t>
   </si>
   <si>
     <t>['13']</t>
@@ -1043,10 +989,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD40"/>
+  <dimension ref="A1:AL40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1161,79 +1107,25 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45783</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="F2" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1248,7 +1140,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L2">
         <v>1.74</v>
@@ -1323,87 +1215,33 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="AK2" t="s">
-        <v>195</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
-      <c r="AM2">
-        <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>0</v>
-      </c>
-      <c r="AO2">
-        <v>7</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2">
-        <v>0</v>
-      </c>
-      <c r="AT2">
-        <v>0</v>
-      </c>
-      <c r="AU2">
-        <v>0</v>
-      </c>
-      <c r="AV2">
-        <v>0</v>
-      </c>
-      <c r="AW2">
-        <v>0</v>
-      </c>
-      <c r="AX2">
-        <v>0</v>
-      </c>
-      <c r="AY2">
-        <v>0</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>1.57</v>
-      </c>
-      <c r="BC2">
-        <v>2.75</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>177</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45783.04166666666</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45783</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="F3" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -1418,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L3">
         <v>3.08</v>
@@ -1493,93 +1331,39 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="AK3" t="s">
-        <v>196</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AO3">
-        <v>7</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3">
-        <v>0</v>
-      </c>
-      <c r="AV3">
-        <v>0</v>
-      </c>
-      <c r="AW3">
-        <v>0</v>
-      </c>
-      <c r="AX3">
-        <v>0</v>
-      </c>
-      <c r="AY3">
-        <v>0</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>2.4</v>
-      </c>
-      <c r="BC3">
-        <v>1.67</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>178</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45783.07986111111</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45783</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="F4" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1588,74 +1372,74 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L4">
-        <v>1.98</v>
+        <v>2.23</v>
       </c>
       <c r="M4">
-        <v>3.11</v>
+        <v>2.87</v>
       </c>
       <c r="N4">
-        <v>3.39</v>
+        <v>3.1</v>
       </c>
       <c r="O4">
+        <v>1.8</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>2.4</v>
+      </c>
+      <c r="R4">
+        <v>1.53</v>
+      </c>
+      <c r="S4">
+        <v>2.38</v>
+      </c>
+      <c r="T4">
+        <v>3.75</v>
+      </c>
+      <c r="U4">
+        <v>1.25</v>
+      </c>
+      <c r="V4">
+        <v>11</v>
+      </c>
+      <c r="W4">
+        <v>1.05</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>1.5</v>
+      </c>
+      <c r="AA4">
+        <v>2.3</v>
+      </c>
+      <c r="AB4">
+        <v>2.48</v>
+      </c>
+      <c r="AC4">
+        <v>1.5</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>2.1</v>
+      </c>
+      <c r="AG4">
         <v>1.67</v>
       </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>2.5</v>
-      </c>
-      <c r="R4">
-        <v>1.44</v>
-      </c>
-      <c r="S4">
-        <v>2.63</v>
-      </c>
-      <c r="T4">
-        <v>3.25</v>
-      </c>
-      <c r="U4">
-        <v>1.33</v>
-      </c>
-      <c r="V4">
-        <v>9</v>
-      </c>
-      <c r="W4">
-        <v>1.07</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>2.1</v>
-      </c>
-      <c r="AC4">
-        <v>1.6</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>1.95</v>
-      </c>
-      <c r="AG4">
-        <v>1.8</v>
-      </c>
       <c r="AH4">
         <v>0</v>
       </c>
@@ -1663,138 +1447,84 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="AK4" t="s">
-        <v>197</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <v>11</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
-      <c r="AR4">
-        <v>0</v>
-      </c>
-      <c r="AS4">
-        <v>0</v>
-      </c>
-      <c r="AT4">
-        <v>0</v>
-      </c>
-      <c r="AU4">
-        <v>0</v>
-      </c>
-      <c r="AV4">
-        <v>0</v>
-      </c>
-      <c r="AW4">
-        <v>0</v>
-      </c>
-      <c r="AX4">
-        <v>0</v>
-      </c>
-      <c r="AY4">
-        <v>0</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>1.67</v>
-      </c>
-      <c r="BC4">
-        <v>2.5</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>156</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45783.08333333334</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45783</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="F5" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L5">
-        <v>2.36</v>
+        <v>2.13</v>
       </c>
       <c r="M5">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="N5">
-        <v>2.64</v>
+        <v>3.1</v>
       </c>
       <c r="O5">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="R5">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S5">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="T5">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="U5">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W5">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
         <v>0</v>
@@ -1809,10 +1539,10 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC5">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1821,10 +1551,10 @@
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AG5">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1833,138 +1563,84 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="AK5" t="s">
-        <v>198</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>0</v>
-      </c>
-      <c r="AO5">
-        <v>5</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <v>0</v>
-      </c>
-      <c r="AW5">
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>1.83</v>
-      </c>
-      <c r="BC5">
-        <v>2.1</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>156</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45783.08333333334</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45783</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="F6" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L6">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="M6">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="N6">
         <v>2.64</v>
       </c>
       <c r="O6">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R6">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S6">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="T6">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="U6">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="V6">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
         <v>0</v>
@@ -1979,10 +1655,10 @@
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC6">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1991,10 +1667,10 @@
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AG6">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -2003,138 +1679,84 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="AK6" t="s">
-        <v>199</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>0</v>
-      </c>
-      <c r="AO6">
-        <v>9</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>1.95</v>
-      </c>
-      <c r="BC6">
-        <v>2.2</v>
-      </c>
-      <c r="BD6" s="3">
+        <v>179</v>
+      </c>
+      <c r="AL6" s="3">
         <v>45783.08333333334</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45783</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="F7" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
         <v>1</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
       </c>
       <c r="J7">
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L7">
-        <v>2.26</v>
+        <v>1.83</v>
       </c>
       <c r="M7">
-        <v>2.98</v>
+        <v>3.23</v>
       </c>
       <c r="N7">
-        <v>2.93</v>
+        <v>3.77</v>
       </c>
       <c r="O7">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="R7">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="S7">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="T7">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="U7">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="V7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
         <v>0</v>
@@ -2143,16 +1765,16 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>2.48</v>
+        <v>1.91</v>
       </c>
       <c r="AC7">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -2161,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG7">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -2173,114 +1795,60 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="AK7" t="s">
-        <v>200</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>0</v>
-      </c>
-      <c r="AO7">
-        <v>7</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7">
-        <v>0</v>
-      </c>
-      <c r="AV7">
-        <v>0</v>
-      </c>
-      <c r="AW7">
-        <v>0</v>
-      </c>
-      <c r="AX7">
-        <v>0</v>
-      </c>
-      <c r="AY7">
-        <v>0</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>1.83</v>
-      </c>
-      <c r="BC7">
-        <v>2.4</v>
-      </c>
-      <c r="BD7" s="3">
+        <v>180</v>
+      </c>
+      <c r="AL7" s="3">
         <v>45783.08333333334</v>
       </c>
     </row>
-    <row r="8" spans="1:56">
+    <row r="8" spans="1:38">
       <c r="A8" s="2">
         <v>45783</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E8" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F8" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L8">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="M8">
-        <v>2.87</v>
+        <v>2.98</v>
       </c>
       <c r="N8">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="O8">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -2289,10 +1857,10 @@
         <v>2.4</v>
       </c>
       <c r="R8">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="S8">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="T8">
         <v>3.75</v>
@@ -2313,10 +1881,10 @@
         <v>0</v>
       </c>
       <c r="Z8">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AA8">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AB8">
         <v>2.48</v>
@@ -2343,120 +1911,66 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="AK8" t="s">
-        <v>174</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>0</v>
-      </c>
-      <c r="AO8">
-        <v>9</v>
-      </c>
-      <c r="AP8">
-        <v>0</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
-      <c r="AS8">
-        <v>0</v>
-      </c>
-      <c r="AT8">
-        <v>0</v>
-      </c>
-      <c r="AU8">
-        <v>0</v>
-      </c>
-      <c r="AV8">
-        <v>0</v>
-      </c>
-      <c r="AW8">
-        <v>0</v>
-      </c>
-      <c r="AX8">
-        <v>0</v>
-      </c>
-      <c r="AY8">
-        <v>0</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>1.8</v>
-      </c>
-      <c r="BC8">
-        <v>2.4</v>
-      </c>
-      <c r="BD8" s="3">
+        <v>181</v>
+      </c>
+      <c r="AL8" s="3">
         <v>45783.08333333334</v>
       </c>
     </row>
-    <row r="9" spans="1:56">
+    <row r="9" spans="1:38">
       <c r="A9" s="2">
         <v>45783</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E9" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="F9" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L9">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="M9">
-        <v>3.04</v>
+        <v>3.21</v>
       </c>
       <c r="N9">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="O9">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R9">
         <v>1.44</v>
@@ -2465,16 +1979,16 @@
         <v>2.63</v>
       </c>
       <c r="T9">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U9">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
         <v>0</v>
@@ -2489,10 +2003,10 @@
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AC9">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AD9">
         <v>0</v>
@@ -2501,132 +2015,78 @@
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG9">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ9" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="AK9" t="s">
-        <v>174</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>0</v>
-      </c>
-      <c r="AN9">
-        <v>0</v>
-      </c>
-      <c r="AO9">
-        <v>9</v>
-      </c>
-      <c r="AP9">
-        <v>0</v>
-      </c>
-      <c r="AQ9">
-        <v>0</v>
-      </c>
-      <c r="AR9">
-        <v>0</v>
-      </c>
-      <c r="AS9">
-        <v>0</v>
-      </c>
-      <c r="AT9">
-        <v>0</v>
-      </c>
-      <c r="AU9">
-        <v>0</v>
-      </c>
-      <c r="AV9">
-        <v>0</v>
-      </c>
-      <c r="AW9">
-        <v>0</v>
-      </c>
-      <c r="AX9">
-        <v>0</v>
-      </c>
-      <c r="AY9">
-        <v>0</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>1.73</v>
-      </c>
-      <c r="BC9">
-        <v>2.4</v>
-      </c>
-      <c r="BD9" s="3">
+        <v>161</v>
+      </c>
+      <c r="AL9" s="3">
         <v>45783.08333333334</v>
       </c>
     </row>
-    <row r="10" spans="1:56">
+    <row r="10" spans="1:38">
       <c r="A10" s="2">
         <v>45783</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E10" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="F10" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <v>1</v>
       </c>
-      <c r="H10">
-        <v>3</v>
-      </c>
       <c r="I10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L10">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="M10">
-        <v>3.23</v>
+        <v>3.11</v>
       </c>
       <c r="N10">
-        <v>3.77</v>
+        <v>3.39</v>
       </c>
       <c r="O10">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="R10">
         <v>1.44</v>
@@ -2635,10 +2095,10 @@
         <v>2.63</v>
       </c>
       <c r="T10">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U10">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V10">
         <v>9</v>
@@ -2659,10 +2119,10 @@
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AC10">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AD10">
         <v>0</v>
@@ -2683,138 +2143,84 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="AK10" t="s">
-        <v>201</v>
-      </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <v>0</v>
-      </c>
-      <c r="AN10">
-        <v>0</v>
-      </c>
-      <c r="AO10">
-        <v>7</v>
-      </c>
-      <c r="AP10">
-        <v>0</v>
-      </c>
-      <c r="AQ10">
-        <v>0</v>
-      </c>
-      <c r="AR10">
-        <v>0</v>
-      </c>
-      <c r="AS10">
-        <v>0</v>
-      </c>
-      <c r="AT10">
-        <v>0</v>
-      </c>
-      <c r="AU10">
-        <v>0</v>
-      </c>
-      <c r="AV10">
-        <v>0</v>
-      </c>
-      <c r="AW10">
-        <v>0</v>
-      </c>
-      <c r="AX10">
-        <v>0</v>
-      </c>
-      <c r="AY10">
-        <v>0</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>1.57</v>
-      </c>
-      <c r="BC10">
-        <v>2.75</v>
-      </c>
-      <c r="BD10" s="3">
+        <v>182</v>
+      </c>
+      <c r="AL10" s="3">
         <v>45783.08333333334</v>
       </c>
     </row>
-    <row r="11" spans="1:56">
+    <row r="11" spans="1:38">
       <c r="A11" s="2">
         <v>45783</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E11" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="F11" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L11">
-        <v>2.03</v>
+        <v>2.58</v>
       </c>
       <c r="M11">
-        <v>3.21</v>
+        <v>2.84</v>
       </c>
       <c r="N11">
-        <v>3.18</v>
+        <v>2.64</v>
       </c>
       <c r="O11">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
+        <v>2.2</v>
+      </c>
+      <c r="R11">
+        <v>1.5</v>
+      </c>
+      <c r="S11">
         <v>2.5</v>
       </c>
-      <c r="R11">
-        <v>1.44</v>
-      </c>
-      <c r="S11">
-        <v>2.63</v>
-      </c>
       <c r="T11">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U11">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
         <v>0</v>
@@ -2829,10 +2235,10 @@
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AC11">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AD11">
         <v>0</v>
@@ -2841,99 +2247,45 @@
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AG11">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AH11">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="AK11" t="s">
-        <v>176</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>0</v>
-      </c>
-      <c r="AN11">
-        <v>0</v>
-      </c>
-      <c r="AO11">
-        <v>14</v>
-      </c>
-      <c r="AP11">
-        <v>0</v>
-      </c>
-      <c r="AQ11">
-        <v>0</v>
-      </c>
-      <c r="AR11">
-        <v>0</v>
-      </c>
-      <c r="AS11">
-        <v>0</v>
-      </c>
-      <c r="AT11">
-        <v>0</v>
-      </c>
-      <c r="AU11">
-        <v>0</v>
-      </c>
-      <c r="AV11">
-        <v>0</v>
-      </c>
-      <c r="AW11">
-        <v>0</v>
-      </c>
-      <c r="AX11">
-        <v>0</v>
-      </c>
-      <c r="AY11">
-        <v>0</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>1.67</v>
-      </c>
-      <c r="BC11">
-        <v>2.5</v>
-      </c>
-      <c r="BD11" s="3">
+        <v>183</v>
+      </c>
+      <c r="AL11" s="3">
         <v>45783.08333333334</v>
       </c>
     </row>
-    <row r="12" spans="1:56">
+    <row r="12" spans="1:38">
       <c r="A12" s="2">
         <v>45783</v>
       </c>
       <c r="B12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s">
         <v>59</v>
       </c>
-      <c r="C12" t="s">
-        <v>77</v>
-      </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F12" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2945,28 +2297,28 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L12">
-        <v>2.37</v>
+        <v>2.93</v>
       </c>
       <c r="M12">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N12">
-        <v>2.57</v>
+        <v>2.22</v>
       </c>
       <c r="O12">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="P12">
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="R12">
         <v>1.5</v>
@@ -2999,10 +2351,10 @@
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC12">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AD12">
         <v>0</v>
@@ -3023,87 +2375,33 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="AK12" t="s">
-        <v>202</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>0</v>
-      </c>
-      <c r="AO12">
-        <v>11</v>
-      </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12">
-        <v>0</v>
-      </c>
-      <c r="AV12">
-        <v>0</v>
-      </c>
-      <c r="AW12">
-        <v>0</v>
-      </c>
-      <c r="AX12">
-        <v>0</v>
-      </c>
-      <c r="AY12">
-        <v>0</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>1.73</v>
-      </c>
-      <c r="BC12">
-        <v>2.4</v>
-      </c>
-      <c r="BD12" s="3">
+        <v>184</v>
+      </c>
+      <c r="AL12" s="3">
         <v>45783.125</v>
       </c>
     </row>
-    <row r="13" spans="1:56">
+    <row r="13" spans="1:38">
       <c r="A13" s="2">
         <v>45783</v>
       </c>
       <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
         <v>59</v>
       </c>
-      <c r="C13" t="s">
-        <v>77</v>
-      </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="F13" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -3118,7 +2416,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L13">
         <v>3.05</v>
@@ -3193,87 +2491,33 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="AK13" t="s">
-        <v>192</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>0</v>
-      </c>
-      <c r="AO13">
-        <v>-1</v>
-      </c>
-      <c r="AP13">
-        <v>0</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
-      </c>
-      <c r="AR13">
-        <v>0</v>
-      </c>
-      <c r="AS13">
-        <v>0</v>
-      </c>
-      <c r="AT13">
-        <v>0</v>
-      </c>
-      <c r="AU13">
-        <v>0</v>
-      </c>
-      <c r="AV13">
-        <v>0</v>
-      </c>
-      <c r="AW13">
-        <v>0</v>
-      </c>
-      <c r="AX13">
-        <v>0</v>
-      </c>
-      <c r="AY13">
-        <v>0</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>2.4</v>
-      </c>
-      <c r="BC13">
-        <v>1.67</v>
-      </c>
-      <c r="BD13" s="3">
+        <v>174</v>
+      </c>
+      <c r="AL13" s="3">
         <v>45783.125</v>
       </c>
     </row>
-    <row r="14" spans="1:56">
+    <row r="14" spans="1:38">
       <c r="A14" s="2">
         <v>45783</v>
       </c>
       <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" t="s">
         <v>59</v>
       </c>
-      <c r="C14" t="s">
-        <v>77</v>
-      </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E14" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="F14" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3285,28 +2529,28 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L14">
-        <v>2.93</v>
+        <v>2.37</v>
       </c>
       <c r="M14">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N14">
-        <v>2.22</v>
+        <v>2.57</v>
       </c>
       <c r="O14">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="P14">
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="R14">
         <v>1.5</v>
@@ -3339,10 +2583,10 @@
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AC14">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AD14">
         <v>0</v>
@@ -3363,87 +2607,33 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="AK14" t="s">
-        <v>203</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-      <c r="AN14">
-        <v>0</v>
-      </c>
-      <c r="AO14">
-        <v>17</v>
-      </c>
-      <c r="AP14">
-        <v>0</v>
-      </c>
-      <c r="AQ14">
-        <v>0</v>
-      </c>
-      <c r="AR14">
-        <v>0</v>
-      </c>
-      <c r="AS14">
-        <v>0</v>
-      </c>
-      <c r="AT14">
-        <v>0</v>
-      </c>
-      <c r="AU14">
-        <v>0</v>
-      </c>
-      <c r="AV14">
-        <v>0</v>
-      </c>
-      <c r="AW14">
-        <v>0</v>
-      </c>
-      <c r="AX14">
-        <v>0</v>
-      </c>
-      <c r="AY14">
-        <v>0</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>2.3</v>
-      </c>
-      <c r="BC14">
-        <v>1.8</v>
-      </c>
-      <c r="BD14" s="3">
+        <v>185</v>
+      </c>
+      <c r="AL14" s="3">
         <v>45783.125</v>
       </c>
     </row>
-    <row r="15" spans="1:56">
+    <row r="15" spans="1:38">
       <c r="A15" s="2">
         <v>45783</v>
       </c>
       <c r="B15" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="F15" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3458,7 +2648,7 @@
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L15">
         <v>2.15</v>
@@ -3533,87 +2723,33 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="AK15" t="s">
-        <v>204</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>0</v>
-      </c>
-      <c r="AN15">
-        <v>0</v>
-      </c>
-      <c r="AO15">
-        <v>12</v>
-      </c>
-      <c r="AP15">
-        <v>0</v>
-      </c>
-      <c r="AQ15">
-        <v>0</v>
-      </c>
-      <c r="AR15">
-        <v>0</v>
-      </c>
-      <c r="AS15">
-        <v>0</v>
-      </c>
-      <c r="AT15">
-        <v>0</v>
-      </c>
-      <c r="AU15">
-        <v>0</v>
-      </c>
-      <c r="AV15">
-        <v>0</v>
-      </c>
-      <c r="AW15">
-        <v>0</v>
-      </c>
-      <c r="AX15">
-        <v>0</v>
-      </c>
-      <c r="AY15">
-        <v>0</v>
-      </c>
-      <c r="AZ15">
-        <v>0</v>
-      </c>
-      <c r="BA15">
-        <v>0</v>
-      </c>
-      <c r="BB15">
-        <v>1.73</v>
-      </c>
-      <c r="BC15">
-        <v>2.5</v>
-      </c>
-      <c r="BD15" s="3">
+        <v>186</v>
+      </c>
+      <c r="AL15" s="3">
         <v>45783.15972222222</v>
       </c>
     </row>
-    <row r="16" spans="1:56">
+    <row r="16" spans="1:38">
       <c r="A16" s="2">
         <v>45783</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="F16" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -3628,7 +2764,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L16">
         <v>2.01</v>
@@ -3703,87 +2839,33 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="AK16" t="s">
-        <v>174</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>0</v>
-      </c>
-      <c r="AO16">
-        <v>15</v>
-      </c>
-      <c r="AP16">
-        <v>0</v>
-      </c>
-      <c r="AQ16">
-        <v>0</v>
-      </c>
-      <c r="AR16">
-        <v>0</v>
-      </c>
-      <c r="AS16">
-        <v>0</v>
-      </c>
-      <c r="AT16">
-        <v>0</v>
-      </c>
-      <c r="AU16">
-        <v>0</v>
-      </c>
-      <c r="AV16">
-        <v>0</v>
-      </c>
-      <c r="AW16">
-        <v>0</v>
-      </c>
-      <c r="AX16">
-        <v>0</v>
-      </c>
-      <c r="AY16">
-        <v>0</v>
-      </c>
-      <c r="AZ16">
-        <v>0</v>
-      </c>
-      <c r="BA16">
-        <v>0</v>
-      </c>
-      <c r="BB16">
-        <v>1.67</v>
-      </c>
-      <c r="BC16">
-        <v>2.5</v>
-      </c>
-      <c r="BD16" s="3">
+        <v>156</v>
+      </c>
+      <c r="AL16" s="3">
         <v>45783.16666666666</v>
       </c>
     </row>
-    <row r="17" spans="1:56">
+    <row r="17" spans="1:38">
       <c r="A17" s="2">
         <v>45783</v>
       </c>
       <c r="B17" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="F17" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -3798,7 +2880,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L17">
         <v>2.18</v>
@@ -3873,87 +2955,33 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="AK17" t="s">
-        <v>205</v>
-      </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
-        <v>0</v>
-      </c>
-      <c r="AN17">
-        <v>0</v>
-      </c>
-      <c r="AO17">
-        <v>12</v>
-      </c>
-      <c r="AP17">
-        <v>0</v>
-      </c>
-      <c r="AQ17">
-        <v>0</v>
-      </c>
-      <c r="AR17">
-        <v>0</v>
-      </c>
-      <c r="AS17">
-        <v>0</v>
-      </c>
-      <c r="AT17">
-        <v>0</v>
-      </c>
-      <c r="AU17">
-        <v>0</v>
-      </c>
-      <c r="AV17">
-        <v>0</v>
-      </c>
-      <c r="AW17">
-        <v>0</v>
-      </c>
-      <c r="AX17">
-        <v>0</v>
-      </c>
-      <c r="AY17">
-        <v>0</v>
-      </c>
-      <c r="AZ17">
-        <v>0</v>
-      </c>
-      <c r="BA17">
-        <v>0</v>
-      </c>
-      <c r="BB17">
-        <v>1.73</v>
-      </c>
-      <c r="BC17">
-        <v>2.25</v>
-      </c>
-      <c r="BD17" s="3">
+        <v>187</v>
+      </c>
+      <c r="AL17" s="3">
         <v>45783.16666666666</v>
       </c>
     </row>
-    <row r="18" spans="1:56">
+    <row r="18" spans="1:38">
       <c r="A18" s="2">
         <v>45783</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" t="s">
         <v>91</v>
       </c>
-      <c r="E18" t="s">
-        <v>109</v>
-      </c>
       <c r="F18" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -3968,7 +2996,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L18">
         <v>2.38</v>
@@ -4043,87 +3071,33 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="AK18" t="s">
-        <v>174</v>
-      </c>
-      <c r="AL18">
-        <v>0</v>
-      </c>
-      <c r="AM18">
-        <v>0</v>
-      </c>
-      <c r="AN18">
-        <v>0</v>
-      </c>
-      <c r="AO18">
-        <v>4</v>
-      </c>
-      <c r="AP18">
-        <v>0</v>
-      </c>
-      <c r="AQ18">
-        <v>0</v>
-      </c>
-      <c r="AR18">
-        <v>0</v>
-      </c>
-      <c r="AS18">
-        <v>0</v>
-      </c>
-      <c r="AT18">
-        <v>0</v>
-      </c>
-      <c r="AU18">
-        <v>0</v>
-      </c>
-      <c r="AV18">
-        <v>0</v>
-      </c>
-      <c r="AW18">
-        <v>0</v>
-      </c>
-      <c r="AX18">
-        <v>0</v>
-      </c>
-      <c r="AY18">
-        <v>0</v>
-      </c>
-      <c r="AZ18">
-        <v>0</v>
-      </c>
-      <c r="BA18">
-        <v>0</v>
-      </c>
-      <c r="BB18">
-        <v>1.91</v>
-      </c>
-      <c r="BC18">
-        <v>2.5</v>
-      </c>
-      <c r="BD18" s="3">
+        <v>156</v>
+      </c>
+      <c r="AL18" s="3">
         <v>45783.16666666666</v>
       </c>
     </row>
-    <row r="19" spans="1:56">
+    <row r="19" spans="1:38">
       <c r="A19" s="2">
         <v>45783</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="F19" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -4138,7 +3112,7 @@
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L19">
         <v>2.14</v>
@@ -4213,87 +3187,33 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="AK19" t="s">
-        <v>206</v>
-      </c>
-      <c r="AL19">
-        <v>0</v>
-      </c>
-      <c r="AM19">
-        <v>0</v>
-      </c>
-      <c r="AN19">
-        <v>0</v>
-      </c>
-      <c r="AO19">
-        <v>10</v>
-      </c>
-      <c r="AP19">
-        <v>0</v>
-      </c>
-      <c r="AQ19">
-        <v>0</v>
-      </c>
-      <c r="AR19">
-        <v>0</v>
-      </c>
-      <c r="AS19">
-        <v>0</v>
-      </c>
-      <c r="AT19">
-        <v>0</v>
-      </c>
-      <c r="AU19">
-        <v>0</v>
-      </c>
-      <c r="AV19">
-        <v>0</v>
-      </c>
-      <c r="AW19">
-        <v>0</v>
-      </c>
-      <c r="AX19">
-        <v>0</v>
-      </c>
-      <c r="AY19">
-        <v>0</v>
-      </c>
-      <c r="AZ19">
-        <v>0</v>
-      </c>
-      <c r="BA19">
-        <v>0</v>
-      </c>
-      <c r="BB19">
-        <v>1.73</v>
-      </c>
-      <c r="BC19">
-        <v>2.38</v>
-      </c>
-      <c r="BD19" s="3">
+        <v>188</v>
+      </c>
+      <c r="AL19" s="3">
         <v>45783.1875</v>
       </c>
     </row>
-    <row r="20" spans="1:56">
+    <row r="20" spans="1:38">
       <c r="A20" s="2">
         <v>45783</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D20" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="F20" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -4308,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L20">
         <v>2.2</v>
@@ -4383,87 +3303,33 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="AK20" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL20">
-        <v>0</v>
-      </c>
-      <c r="AM20">
-        <v>0</v>
-      </c>
-      <c r="AN20">
-        <v>0</v>
-      </c>
-      <c r="AO20">
-        <v>12</v>
-      </c>
-      <c r="AP20">
-        <v>0</v>
-      </c>
-      <c r="AQ20">
-        <v>0</v>
-      </c>
-      <c r="AR20">
-        <v>0</v>
-      </c>
-      <c r="AS20">
-        <v>0</v>
-      </c>
-      <c r="AT20">
-        <v>0</v>
-      </c>
-      <c r="AU20">
-        <v>0</v>
-      </c>
-      <c r="AV20">
-        <v>0</v>
-      </c>
-      <c r="AW20">
-        <v>0</v>
-      </c>
-      <c r="AX20">
-        <v>0</v>
-      </c>
-      <c r="AY20">
-        <v>0</v>
-      </c>
-      <c r="AZ20">
-        <v>0</v>
-      </c>
-      <c r="BA20">
-        <v>0</v>
-      </c>
-      <c r="BB20">
-        <v>1.73</v>
-      </c>
-      <c r="BC20">
-        <v>2.25</v>
-      </c>
-      <c r="BD20" s="3">
+        <v>189</v>
+      </c>
+      <c r="AL20" s="3">
         <v>45783.29166666666</v>
       </c>
     </row>
-    <row r="21" spans="1:56">
+    <row r="21" spans="1:38">
       <c r="A21" s="2">
         <v>45783</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D21" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E21" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="F21" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -4478,7 +3344,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L21">
         <v>4.6</v>
@@ -4553,87 +3419,33 @@
         <v>0</v>
       </c>
       <c r="AJ21" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="AK21" t="s">
-        <v>208</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>0</v>
-      </c>
-      <c r="AN21">
-        <v>0</v>
-      </c>
-      <c r="AO21">
-        <v>9</v>
-      </c>
-      <c r="AP21">
-        <v>0</v>
-      </c>
-      <c r="AQ21">
-        <v>0</v>
-      </c>
-      <c r="AR21">
-        <v>0</v>
-      </c>
-      <c r="AS21">
-        <v>0</v>
-      </c>
-      <c r="AT21">
-        <v>0</v>
-      </c>
-      <c r="AU21">
-        <v>0</v>
-      </c>
-      <c r="AV21">
-        <v>0</v>
-      </c>
-      <c r="AW21">
-        <v>0</v>
-      </c>
-      <c r="AX21">
-        <v>0</v>
-      </c>
-      <c r="AY21">
-        <v>0</v>
-      </c>
-      <c r="AZ21">
-        <v>0</v>
-      </c>
-      <c r="BA21">
-        <v>0</v>
-      </c>
-      <c r="BB21">
-        <v>2.88</v>
-      </c>
-      <c r="BC21">
-        <v>1.53</v>
-      </c>
-      <c r="BD21" s="3">
+        <v>190</v>
+      </c>
+      <c r="AL21" s="3">
         <v>45783.29166666666</v>
       </c>
     </row>
-    <row r="22" spans="1:56">
+    <row r="22" spans="1:38">
       <c r="A22" s="2">
         <v>45783</v>
       </c>
       <c r="B22" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E22" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="F22" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -4648,7 +3460,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L22">
         <v>5.3</v>
@@ -4723,102 +3535,48 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="AK22" t="s">
-        <v>209</v>
-      </c>
-      <c r="AL22">
-        <v>0</v>
-      </c>
-      <c r="AM22">
-        <v>0</v>
-      </c>
-      <c r="AN22">
-        <v>0</v>
-      </c>
-      <c r="AO22">
-        <v>-1</v>
-      </c>
-      <c r="AP22">
-        <v>0</v>
-      </c>
-      <c r="AQ22">
-        <v>0</v>
-      </c>
-      <c r="AR22">
-        <v>0</v>
-      </c>
-      <c r="AS22">
-        <v>0</v>
-      </c>
-      <c r="AT22">
-        <v>0</v>
-      </c>
-      <c r="AU22">
-        <v>0</v>
-      </c>
-      <c r="AV22">
-        <v>0</v>
-      </c>
-      <c r="AW22">
-        <v>0</v>
-      </c>
-      <c r="AX22">
-        <v>0</v>
-      </c>
-      <c r="AY22">
-        <v>0</v>
-      </c>
-      <c r="AZ22">
-        <v>0</v>
-      </c>
-      <c r="BA22">
-        <v>0</v>
-      </c>
-      <c r="BB22">
-        <v>3</v>
-      </c>
-      <c r="BC22">
-        <v>1.36</v>
-      </c>
-      <c r="BD22" s="3">
+        <v>191</v>
+      </c>
+      <c r="AL22" s="3">
         <v>45783.33333333334</v>
       </c>
     </row>
-    <row r="23" spans="1:56">
+    <row r="23" spans="1:38">
       <c r="A23" s="2">
         <v>45783</v>
       </c>
       <c r="B23" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E23" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="F23" t="s">
+        <v>135</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23" t="s">
         <v>153</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23" t="s">
-        <v>171</v>
       </c>
       <c r="L23">
         <v>1.93</v>
@@ -4893,87 +3651,33 @@
         <v>0</v>
       </c>
       <c r="AJ23" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="AK23" t="s">
-        <v>174</v>
-      </c>
-      <c r="AL23">
-        <v>0</v>
-      </c>
-      <c r="AM23">
-        <v>0</v>
-      </c>
-      <c r="AN23">
-        <v>0</v>
-      </c>
-      <c r="AO23">
-        <v>15</v>
-      </c>
-      <c r="AP23">
-        <v>0</v>
-      </c>
-      <c r="AQ23">
-        <v>0</v>
-      </c>
-      <c r="AR23">
-        <v>0</v>
-      </c>
-      <c r="AS23">
-        <v>0</v>
-      </c>
-      <c r="AT23">
-        <v>0</v>
-      </c>
-      <c r="AU23">
-        <v>0</v>
-      </c>
-      <c r="AV23">
-        <v>0</v>
-      </c>
-      <c r="AW23">
-        <v>0</v>
-      </c>
-      <c r="AX23">
-        <v>0</v>
-      </c>
-      <c r="AY23">
-        <v>0</v>
-      </c>
-      <c r="AZ23">
-        <v>0</v>
-      </c>
-      <c r="BA23">
-        <v>0</v>
-      </c>
-      <c r="BB23">
-        <v>1.53</v>
-      </c>
-      <c r="BC23">
-        <v>2.5</v>
-      </c>
-      <c r="BD23" s="3">
+        <v>156</v>
+      </c>
+      <c r="AL23" s="3">
         <v>45783.35763888889</v>
       </c>
     </row>
-    <row r="24" spans="1:56">
+    <row r="24" spans="1:38">
       <c r="A24" s="2">
         <v>45783</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="E24" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="F24" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -4988,7 +3692,7 @@
         <v>2</v>
       </c>
       <c r="K24" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L24">
         <v>2.75</v>
@@ -5063,87 +3767,33 @@
         <v>1.02</v>
       </c>
       <c r="AJ24" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="AK24" t="s">
-        <v>210</v>
-      </c>
-      <c r="AL24">
-        <v>1.4</v>
-      </c>
-      <c r="AM24">
-        <v>1.35</v>
-      </c>
-      <c r="AN24">
-        <v>1.35</v>
-      </c>
-      <c r="AO24">
-        <v>7</v>
-      </c>
-      <c r="AP24">
-        <v>1.55</v>
-      </c>
-      <c r="AQ24">
-        <v>1.91</v>
-      </c>
-      <c r="AR24">
-        <v>2.92</v>
-      </c>
-      <c r="AS24">
-        <v>3.22</v>
-      </c>
-      <c r="AT24">
-        <v>4.45</v>
-      </c>
-      <c r="AU24">
-        <v>2.36</v>
-      </c>
-      <c r="AV24">
-        <v>1.83</v>
-      </c>
-      <c r="AW24">
-        <v>1.49</v>
-      </c>
-      <c r="AX24">
-        <v>1.28</v>
-      </c>
-      <c r="AY24">
-        <v>1.15</v>
-      </c>
-      <c r="AZ24">
-        <v>0</v>
-      </c>
-      <c r="BA24">
-        <v>0</v>
-      </c>
-      <c r="BB24">
-        <v>2.67</v>
-      </c>
-      <c r="BC24">
-        <v>1.75</v>
-      </c>
-      <c r="BD24" s="3">
+        <v>192</v>
+      </c>
+      <c r="AL24" s="3">
         <v>45783.45833333334</v>
       </c>
     </row>
-    <row r="25" spans="1:56">
+    <row r="25" spans="1:38">
       <c r="A25" s="2">
         <v>45783</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="D25" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="E25" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="F25" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -5158,7 +3808,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L25">
         <v>2.73</v>
@@ -5233,87 +3883,33 @@
         <v>1.02</v>
       </c>
       <c r="AJ25" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="AK25" t="s">
-        <v>174</v>
-      </c>
-      <c r="AL25">
-        <v>1.3</v>
-      </c>
-      <c r="AM25">
-        <v>1.47</v>
-      </c>
-      <c r="AN25">
-        <v>1.49</v>
-      </c>
-      <c r="AO25">
-        <v>3</v>
-      </c>
-      <c r="AP25">
-        <v>1.42</v>
-      </c>
-      <c r="AQ25">
-        <v>1.7</v>
-      </c>
-      <c r="AR25">
-        <v>2.1</v>
-      </c>
-      <c r="AS25">
-        <v>2.8</v>
-      </c>
-      <c r="AT25">
-        <v>3.6</v>
-      </c>
-      <c r="AU25">
-        <v>2.62</v>
-      </c>
-      <c r="AV25">
-        <v>2</v>
-      </c>
-      <c r="AW25">
-        <v>1.65</v>
-      </c>
-      <c r="AX25">
-        <v>1.38</v>
-      </c>
-      <c r="AY25">
-        <v>1.23</v>
-      </c>
-      <c r="AZ25">
-        <v>0</v>
-      </c>
-      <c r="BA25">
-        <v>0</v>
-      </c>
-      <c r="BB25">
-        <v>2.1</v>
-      </c>
-      <c r="BC25">
-        <v>2.4</v>
-      </c>
-      <c r="BD25" s="3">
+        <v>156</v>
+      </c>
+      <c r="AL25" s="3">
         <v>45783.45833333334</v>
       </c>
     </row>
-    <row r="26" spans="1:56">
+    <row r="26" spans="1:38">
       <c r="A26" s="2">
         <v>45783</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="D26" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="F26" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5328,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L26">
         <v>2.6</v>
@@ -5403,87 +3999,33 @@
         <v>1.03</v>
       </c>
       <c r="AJ26" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="AK26" t="s">
-        <v>174</v>
-      </c>
-      <c r="AL26">
-        <v>1.32</v>
-      </c>
-      <c r="AM26">
-        <v>0</v>
-      </c>
-      <c r="AN26">
-        <v>1.33</v>
-      </c>
-      <c r="AO26">
-        <v>11</v>
-      </c>
-      <c r="AP26">
-        <v>0</v>
-      </c>
-      <c r="AQ26">
-        <v>0</v>
-      </c>
-      <c r="AR26">
-        <v>0</v>
-      </c>
-      <c r="AS26">
-        <v>0</v>
-      </c>
-      <c r="AT26">
-        <v>0</v>
-      </c>
-      <c r="AU26">
-        <v>0</v>
-      </c>
-      <c r="AV26">
-        <v>0</v>
-      </c>
-      <c r="AW26">
-        <v>0</v>
-      </c>
-      <c r="AX26">
-        <v>0</v>
-      </c>
-      <c r="AY26">
-        <v>0</v>
-      </c>
-      <c r="AZ26">
-        <v>0</v>
-      </c>
-      <c r="BA26">
-        <v>0</v>
-      </c>
-      <c r="BB26">
-        <v>2.3</v>
-      </c>
-      <c r="BC26">
-        <v>1.83</v>
-      </c>
-      <c r="BD26" s="3">
+        <v>156</v>
+      </c>
+      <c r="AL26" s="3">
         <v>45783.5</v>
       </c>
     </row>
-    <row r="27" spans="1:56">
+    <row r="27" spans="1:38">
       <c r="A27" s="2">
         <v>45783</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D27" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="F27" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -5498,7 +4040,7 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L27">
         <v>2</v>
@@ -5573,87 +4115,33 @@
         <v>1.2</v>
       </c>
       <c r="AJ27" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="AK27" t="s">
-        <v>211</v>
-      </c>
-      <c r="AL27">
-        <v>1.25</v>
-      </c>
-      <c r="AM27">
-        <v>0</v>
-      </c>
-      <c r="AN27">
-        <v>1.75</v>
-      </c>
-      <c r="AO27">
-        <v>7</v>
-      </c>
-      <c r="AP27">
-        <v>1.18</v>
-      </c>
-      <c r="AQ27">
-        <v>1.38</v>
-      </c>
-      <c r="AR27">
-        <v>1.67</v>
-      </c>
-      <c r="AS27">
-        <v>2.1</v>
-      </c>
-      <c r="AT27">
-        <v>2.63</v>
-      </c>
-      <c r="AU27">
-        <v>3.68</v>
-      </c>
-      <c r="AV27">
-        <v>2.65</v>
-      </c>
-      <c r="AW27">
-        <v>2.05</v>
-      </c>
-      <c r="AX27">
-        <v>1.65</v>
-      </c>
-      <c r="AY27">
-        <v>1.42</v>
-      </c>
-      <c r="AZ27">
-        <v>0</v>
-      </c>
-      <c r="BA27">
-        <v>0</v>
-      </c>
-      <c r="BB27">
-        <v>1.8</v>
-      </c>
-      <c r="BC27">
-        <v>2.1</v>
-      </c>
-      <c r="BD27" s="3">
+        <v>193</v>
+      </c>
+      <c r="AL27" s="3">
         <v>45783.54166666666</v>
       </c>
     </row>
-    <row r="28" spans="1:56">
+    <row r="28" spans="1:38">
       <c r="A28" s="2">
         <v>45783</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="D28" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="F28" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="G28">
         <v>3</v>
@@ -5668,7 +4156,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L28">
         <v>2.05</v>
@@ -5743,597 +4231,381 @@
         <v>1.07</v>
       </c>
       <c r="AJ28" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="AK28" t="s">
-        <v>212</v>
-      </c>
-      <c r="AL28">
-        <v>1.33</v>
-      </c>
-      <c r="AM28">
-        <v>1.32</v>
-      </c>
-      <c r="AN28">
-        <v>1.57</v>
-      </c>
-      <c r="AO28">
-        <v>12</v>
-      </c>
-      <c r="AP28">
-        <v>1.32</v>
-      </c>
-      <c r="AQ28">
-        <v>1.55</v>
-      </c>
-      <c r="AR28">
-        <v>2.12</v>
-      </c>
-      <c r="AS28">
-        <v>2.37</v>
-      </c>
-      <c r="AT28">
-        <v>3.07</v>
-      </c>
-      <c r="AU28">
-        <v>3.2</v>
-      </c>
-      <c r="AV28">
-        <v>2.35</v>
-      </c>
-      <c r="AW28">
-        <v>1.87</v>
-      </c>
-      <c r="AX28">
-        <v>1.55</v>
-      </c>
-      <c r="AY28">
-        <v>1.32</v>
-      </c>
-      <c r="AZ28">
-        <v>0</v>
-      </c>
-      <c r="BA28">
-        <v>0</v>
-      </c>
-      <c r="BB28">
-        <v>2.02</v>
-      </c>
-      <c r="BC28">
-        <v>2.04</v>
-      </c>
-      <c r="BD28" s="3">
+        <v>194</v>
+      </c>
+      <c r="AL28" s="3">
         <v>45783.5625</v>
       </c>
     </row>
-    <row r="29" spans="1:56">
+    <row r="29" spans="1:38">
       <c r="A29" s="2">
         <v>45783</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="D29" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F29" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29">
         <v>0</v>
       </c>
       <c r="J29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L29">
-        <v>3.09</v>
+        <v>2.5</v>
       </c>
       <c r="M29">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="N29">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="O29">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="P29">
-        <v>11</v>
+        <v>4.8</v>
       </c>
       <c r="Q29">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="R29">
-        <v>1.33</v>
+        <v>1.72</v>
       </c>
       <c r="S29">
-        <v>3.25</v>
+        <v>2.16</v>
       </c>
       <c r="T29">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="U29">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="W29">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X29">
+        <v>1.11</v>
+      </c>
+      <c r="Y29">
+        <v>5.3</v>
+      </c>
+      <c r="Z29">
+        <v>1.78</v>
+      </c>
+      <c r="AA29">
+        <v>2.08</v>
+      </c>
+      <c r="AB29">
+        <v>2.9</v>
+      </c>
+      <c r="AC29">
+        <v>1.35</v>
+      </c>
+      <c r="AD29">
+        <v>7.1</v>
+      </c>
+      <c r="AE29">
         <v>1.04</v>
       </c>
-      <c r="Y29">
-        <v>10</v>
-      </c>
-      <c r="Z29">
-        <v>1.22</v>
-      </c>
-      <c r="AA29">
-        <v>4.2</v>
-      </c>
-      <c r="AB29">
-        <v>1.65</v>
-      </c>
-      <c r="AC29">
-        <v>2.05</v>
-      </c>
-      <c r="AD29">
-        <v>2.7</v>
-      </c>
-      <c r="AE29">
-        <v>1.45</v>
-      </c>
       <c r="AF29">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="AG29">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AH29">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="AI29">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="AJ29" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="AK29" t="s">
-        <v>213</v>
-      </c>
-      <c r="AL29">
-        <v>1.68</v>
-      </c>
-      <c r="AM29">
-        <v>1.27</v>
-      </c>
-      <c r="AN29">
-        <v>1.34</v>
-      </c>
-      <c r="AO29">
-        <v>-1</v>
-      </c>
-      <c r="AP29">
-        <v>1.21</v>
-      </c>
-      <c r="AQ29">
-        <v>1.41</v>
-      </c>
-      <c r="AR29">
-        <v>1.68</v>
-      </c>
-      <c r="AS29">
-        <v>2.07</v>
-      </c>
-      <c r="AT29">
-        <v>2.6</v>
-      </c>
-      <c r="AU29">
-        <v>3.75</v>
-      </c>
-      <c r="AV29">
-        <v>2.7</v>
-      </c>
-      <c r="AW29">
-        <v>2.11</v>
-      </c>
-      <c r="AX29">
-        <v>1.7</v>
-      </c>
-      <c r="AY29">
-        <v>1.44</v>
-      </c>
-      <c r="AZ29">
-        <v>0</v>
-      </c>
-      <c r="BA29">
-        <v>0</v>
-      </c>
-      <c r="BB29">
-        <v>2.25</v>
-      </c>
-      <c r="BC29">
-        <v>1.67</v>
-      </c>
-      <c r="BD29" s="3">
+        <v>156</v>
+      </c>
+      <c r="AL29" s="3">
         <v>45783.58333333334</v>
       </c>
     </row>
-    <row r="30" spans="1:56">
+    <row r="30" spans="1:38">
       <c r="A30" s="2">
         <v>45783</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C30" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="D30" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="F30" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
         <v>1</v>
       </c>
-      <c r="J30">
-        <v>2</v>
-      </c>
       <c r="K30" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L30">
-        <v>2.31</v>
+        <v>3.09</v>
       </c>
       <c r="M30">
-        <v>3.31</v>
+        <v>3.6</v>
       </c>
       <c r="N30">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="O30">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q30">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="R30">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S30">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T30">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U30">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W30">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB30">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AC30">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF30">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG30">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI30">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ30" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="AK30" t="s">
-        <v>214</v>
-      </c>
-      <c r="AL30">
-        <v>0</v>
-      </c>
-      <c r="AM30">
-        <v>0</v>
-      </c>
-      <c r="AN30">
-        <v>0</v>
-      </c>
-      <c r="AO30">
-        <v>-1</v>
-      </c>
-      <c r="AP30">
-        <v>0</v>
-      </c>
-      <c r="AQ30">
-        <v>0</v>
-      </c>
-      <c r="AR30">
-        <v>0</v>
-      </c>
-      <c r="AS30">
-        <v>0</v>
-      </c>
-      <c r="AT30">
-        <v>0</v>
-      </c>
-      <c r="AU30">
-        <v>0</v>
-      </c>
-      <c r="AV30">
-        <v>0</v>
-      </c>
-      <c r="AW30">
-        <v>0</v>
-      </c>
-      <c r="AX30">
-        <v>0</v>
-      </c>
-      <c r="AY30">
-        <v>0</v>
-      </c>
-      <c r="AZ30">
-        <v>0</v>
-      </c>
-      <c r="BA30">
-        <v>0</v>
-      </c>
-      <c r="BB30">
-        <v>1.83</v>
-      </c>
-      <c r="BC30">
-        <v>2.1</v>
-      </c>
-      <c r="BD30" s="3">
+        <v>195</v>
+      </c>
+      <c r="AL30" s="3">
         <v>45783.58333333334</v>
       </c>
     </row>
-    <row r="31" spans="1:56">
+    <row r="31" spans="1:38">
       <c r="A31" s="2">
         <v>45783</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C31" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D31" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="E31" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="F31" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K31" t="s">
+        <v>153</v>
+      </c>
+      <c r="L31">
+        <v>2.31</v>
+      </c>
+      <c r="M31">
+        <v>3.31</v>
+      </c>
+      <c r="N31">
+        <v>2.6</v>
+      </c>
+      <c r="O31">
+        <v>1.83</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>2.1</v>
+      </c>
+      <c r="R31">
+        <v>1.36</v>
+      </c>
+      <c r="S31">
+        <v>3</v>
+      </c>
+      <c r="T31">
+        <v>2.75</v>
+      </c>
+      <c r="U31">
+        <v>1.4</v>
+      </c>
+      <c r="V31">
+        <v>7</v>
+      </c>
+      <c r="W31">
+        <v>1.1</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>1.83</v>
+      </c>
+      <c r="AC31">
+        <v>1.87</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>1.7</v>
+      </c>
+      <c r="AG31">
+        <v>2.05</v>
+      </c>
+      <c r="AH31">
+        <v>0</v>
+      </c>
+      <c r="AI31">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="s">
         <v>171</v>
       </c>
-      <c r="L31">
-        <v>2.5</v>
-      </c>
-      <c r="M31">
-        <v>2.7</v>
-      </c>
-      <c r="N31">
-        <v>3</v>
-      </c>
-      <c r="O31">
-        <v>1.8</v>
-      </c>
-      <c r="P31">
-        <v>4.8</v>
-      </c>
-      <c r="Q31">
-        <v>2.75</v>
-      </c>
-      <c r="R31">
-        <v>1.72</v>
-      </c>
-      <c r="S31">
-        <v>2.16</v>
-      </c>
-      <c r="T31">
-        <v>4.1</v>
-      </c>
-      <c r="U31">
-        <v>1.17</v>
-      </c>
-      <c r="V31">
-        <v>17</v>
-      </c>
-      <c r="W31">
-        <v>1.03</v>
-      </c>
-      <c r="X31">
-        <v>1.11</v>
-      </c>
-      <c r="Y31">
-        <v>5.3</v>
-      </c>
-      <c r="Z31">
-        <v>1.78</v>
-      </c>
-      <c r="AA31">
-        <v>2.08</v>
-      </c>
-      <c r="AB31">
-        <v>2.9</v>
-      </c>
-      <c r="AC31">
-        <v>1.35</v>
-      </c>
-      <c r="AD31">
-        <v>7.1</v>
-      </c>
-      <c r="AE31">
-        <v>1.04</v>
-      </c>
-      <c r="AF31">
-        <v>2.2</v>
-      </c>
-      <c r="AG31">
-        <v>1.55</v>
-      </c>
-      <c r="AH31">
-        <v>15.5</v>
-      </c>
-      <c r="AI31">
-        <v>1.02</v>
-      </c>
-      <c r="AJ31" t="s">
-        <v>174</v>
-      </c>
       <c r="AK31" t="s">
-        <v>174</v>
-      </c>
-      <c r="AL31">
-        <v>1.42</v>
-      </c>
-      <c r="AM31">
-        <v>1.41</v>
-      </c>
-      <c r="AN31">
-        <v>1.45</v>
-      </c>
-      <c r="AO31">
-        <v>6</v>
-      </c>
-      <c r="AP31">
-        <v>1.53</v>
-      </c>
-      <c r="AQ31">
-        <v>1.91</v>
-      </c>
-      <c r="AR31">
-        <v>2.4</v>
-      </c>
-      <c r="AS31">
-        <v>3.2</v>
-      </c>
-      <c r="AT31">
-        <v>4.33</v>
-      </c>
-      <c r="AU31">
-        <v>2.38</v>
-      </c>
-      <c r="AV31">
-        <v>1.8</v>
-      </c>
-      <c r="AW31">
-        <v>1.5</v>
-      </c>
-      <c r="AX31">
-        <v>1.3</v>
-      </c>
-      <c r="AY31">
-        <v>1.18</v>
-      </c>
-      <c r="AZ31">
-        <v>0</v>
-      </c>
-      <c r="BA31">
-        <v>0</v>
-      </c>
-      <c r="BB31">
-        <v>1.8</v>
-      </c>
-      <c r="BC31">
-        <v>2.75</v>
-      </c>
-      <c r="BD31" s="3">
+        <v>196</v>
+      </c>
+      <c r="AL31" s="3">
         <v>45783.58333333334</v>
       </c>
     </row>
-    <row r="32" spans="1:56">
+    <row r="32" spans="1:38">
       <c r="A32" s="2">
         <v>45783</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C32" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="D32" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="E32" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="F32" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -6348,7 +4620,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L32">
         <v>5.9</v>
@@ -6423,87 +4695,33 @@
         <v>1</v>
       </c>
       <c r="AJ32" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="AK32" t="s">
-        <v>215</v>
-      </c>
-      <c r="AL32">
-        <v>2.32</v>
-      </c>
-      <c r="AM32">
-        <v>1.24</v>
-      </c>
-      <c r="AN32">
-        <v>1.07</v>
-      </c>
-      <c r="AO32">
-        <v>11</v>
-      </c>
-      <c r="AP32">
-        <v>1.67</v>
-      </c>
-      <c r="AQ32">
-        <v>2.08</v>
-      </c>
-      <c r="AR32">
-        <v>2.7</v>
-      </c>
-      <c r="AS32">
-        <v>3.65</v>
-      </c>
-      <c r="AT32">
-        <v>5.1</v>
-      </c>
-      <c r="AU32">
-        <v>2.07</v>
-      </c>
-      <c r="AV32">
-        <v>1.66</v>
-      </c>
-      <c r="AW32">
-        <v>1.4</v>
-      </c>
-      <c r="AX32">
-        <v>1.23</v>
-      </c>
-      <c r="AY32">
-        <v>1.13</v>
-      </c>
-      <c r="AZ32">
-        <v>0</v>
-      </c>
-      <c r="BA32">
-        <v>0</v>
-      </c>
-      <c r="BB32">
-        <v>4.33</v>
-      </c>
-      <c r="BC32">
-        <v>1.4</v>
-      </c>
-      <c r="BD32" s="3">
+        <v>197</v>
+      </c>
+      <c r="AL32" s="3">
         <v>45783.60416666666</v>
       </c>
     </row>
-    <row r="33" spans="1:56">
+    <row r="33" spans="1:38">
       <c r="A33" s="2">
         <v>45783</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="C33" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="D33" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="E33" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F33" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="G33">
         <v>4</v>
@@ -6518,7 +4736,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L33">
         <v>2.77</v>
@@ -6593,90 +4811,36 @@
         <v>1.3</v>
       </c>
       <c r="AJ33" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="AK33" t="s">
-        <v>216</v>
-      </c>
-      <c r="AL33">
-        <v>1.68</v>
-      </c>
-      <c r="AM33">
-        <v>1.25</v>
-      </c>
-      <c r="AN33">
-        <v>1.38</v>
-      </c>
-      <c r="AO33">
-        <v>12</v>
-      </c>
-      <c r="AP33">
-        <v>1.21</v>
-      </c>
-      <c r="AQ33">
-        <v>1.38</v>
-      </c>
-      <c r="AR33">
-        <v>1.63</v>
-      </c>
-      <c r="AS33">
-        <v>1.98</v>
-      </c>
-      <c r="AT33">
-        <v>2.5</v>
-      </c>
-      <c r="AU33">
-        <v>3.8</v>
-      </c>
-      <c r="AV33">
-        <v>2.7</v>
-      </c>
-      <c r="AW33">
-        <v>2.1</v>
-      </c>
-      <c r="AX33">
-        <v>1.72</v>
-      </c>
-      <c r="AY33">
-        <v>1.46</v>
-      </c>
-      <c r="AZ33">
-        <v>0</v>
-      </c>
-      <c r="BA33">
-        <v>0</v>
-      </c>
-      <c r="BB33">
-        <v>2.1</v>
-      </c>
-      <c r="BC33">
-        <v>1.67</v>
-      </c>
-      <c r="BD33" s="3">
+        <v>198</v>
+      </c>
+      <c r="AL33" s="3">
         <v>45783.66666666666</v>
       </c>
     </row>
-    <row r="34" spans="1:56">
+    <row r="34" spans="1:38">
       <c r="A34" s="2">
         <v>45783</v>
       </c>
       <c r="B34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" t="s">
         <v>73</v>
       </c>
-      <c r="C34" t="s">
-        <v>89</v>
-      </c>
-      <c r="D34" t="s">
-        <v>91</v>
-      </c>
       <c r="E34" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="F34" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34">
         <v>2</v>
@@ -6688,61 +4852,61 @@
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L34">
-        <v>3.17</v>
+        <v>5.7</v>
       </c>
       <c r="M34">
-        <v>2.92</v>
+        <v>3.73</v>
       </c>
       <c r="N34">
-        <v>2.17</v>
+        <v>1.48</v>
       </c>
       <c r="O34">
+        <v>4</v>
+      </c>
+      <c r="P34">
+        <v>7</v>
+      </c>
+      <c r="Q34">
+        <v>1.36</v>
+      </c>
+      <c r="R34">
+        <v>1.5</v>
+      </c>
+      <c r="S34">
         <v>2.5</v>
       </c>
-      <c r="P34">
-        <v>6.25</v>
-      </c>
-      <c r="Q34">
-        <v>1.8</v>
-      </c>
-      <c r="R34">
+      <c r="T34">
+        <v>3.4</v>
+      </c>
+      <c r="U34">
+        <v>1.3</v>
+      </c>
+      <c r="V34">
+        <v>10</v>
+      </c>
+      <c r="W34">
+        <v>1.06</v>
+      </c>
+      <c r="X34">
+        <v>1.07</v>
+      </c>
+      <c r="Y34">
+        <v>8</v>
+      </c>
+      <c r="Z34">
+        <v>1.44</v>
+      </c>
+      <c r="AA34">
+        <v>2.7</v>
+      </c>
+      <c r="AB34">
+        <v>2.25</v>
+      </c>
+      <c r="AC34">
         <v>1.53</v>
-      </c>
-      <c r="S34">
-        <v>2.38</v>
-      </c>
-      <c r="T34">
-        <v>3.5</v>
-      </c>
-      <c r="U34">
-        <v>1.29</v>
-      </c>
-      <c r="V34">
-        <v>11</v>
-      </c>
-      <c r="W34">
-        <v>1.05</v>
-      </c>
-      <c r="X34">
-        <v>1.1</v>
-      </c>
-      <c r="Y34">
-        <v>6.5</v>
-      </c>
-      <c r="Z34">
-        <v>1.49</v>
-      </c>
-      <c r="AA34">
-        <v>2.6</v>
-      </c>
-      <c r="AB34">
-        <v>2.37</v>
-      </c>
-      <c r="AC34">
-        <v>1.48</v>
       </c>
       <c r="AD34">
         <v>4.75</v>
@@ -6751,13 +4915,13 @@
         <v>1.18</v>
       </c>
       <c r="AF34">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="AG34">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AH34">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="AI34">
         <v>1.05</v>
@@ -6766,90 +4930,36 @@
         <v>174</v>
       </c>
       <c r="AK34" t="s">
-        <v>217</v>
-      </c>
-      <c r="AL34">
-        <v>1.53</v>
-      </c>
-      <c r="AM34">
-        <v>1.36</v>
-      </c>
-      <c r="AN34">
-        <v>1.35</v>
-      </c>
-      <c r="AO34">
-        <v>-1</v>
-      </c>
-      <c r="AP34">
-        <v>1.35</v>
-      </c>
-      <c r="AQ34">
-        <v>1.63</v>
-      </c>
-      <c r="AR34">
-        <v>2</v>
-      </c>
-      <c r="AS34">
-        <v>2.55</v>
-      </c>
-      <c r="AT34">
-        <v>3.4</v>
-      </c>
-      <c r="AU34">
-        <v>2.88</v>
-      </c>
-      <c r="AV34">
-        <v>2.12</v>
-      </c>
-      <c r="AW34">
-        <v>1.71</v>
-      </c>
-      <c r="AX34">
-        <v>1.44</v>
-      </c>
-      <c r="AY34">
-        <v>1.26</v>
-      </c>
-      <c r="AZ34">
-        <v>0</v>
-      </c>
-      <c r="BA34">
-        <v>0</v>
-      </c>
-      <c r="BB34">
-        <v>2.5</v>
-      </c>
-      <c r="BC34">
-        <v>1.8</v>
-      </c>
-      <c r="BD34" s="3">
+        <v>199</v>
+      </c>
+      <c r="AL34" s="3">
         <v>45783.79166666666</v>
       </c>
     </row>
-    <row r="35" spans="1:56">
+    <row r="35" spans="1:38">
       <c r="A35" s="2">
         <v>45783</v>
       </c>
       <c r="B35" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" t="s">
         <v>73</v>
       </c>
-      <c r="C35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D35" t="s">
-        <v>91</v>
-      </c>
       <c r="E35" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="F35" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -6858,25 +4968,25 @@
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L35">
-        <v>5.7</v>
+        <v>3.07</v>
       </c>
       <c r="M35">
-        <v>3.73</v>
+        <v>3.02</v>
       </c>
       <c r="N35">
-        <v>1.48</v>
+        <v>2.16</v>
       </c>
       <c r="O35">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="P35">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="Q35">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="R35">
         <v>1.5</v>
@@ -6897,13 +5007,13 @@
         <v>1.06</v>
       </c>
       <c r="X35">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Y35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z35">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AA35">
         <v>2.7</v>
@@ -6915,16 +5025,16 @@
         <v>1.53</v>
       </c>
       <c r="AD35">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AE35">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF35">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="AG35">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AH35">
         <v>9</v>
@@ -6933,93 +5043,39 @@
         <v>1.05</v>
       </c>
       <c r="AJ35" t="s">
-        <v>192</v>
+        <v>156</v>
       </c>
       <c r="AK35" t="s">
-        <v>218</v>
-      </c>
-      <c r="AL35">
-        <v>2.37</v>
-      </c>
-      <c r="AM35">
-        <v>1.26</v>
-      </c>
-      <c r="AN35">
-        <v>1.11</v>
-      </c>
-      <c r="AO35">
-        <v>-1</v>
-      </c>
-      <c r="AP35">
-        <v>1.34</v>
-      </c>
-      <c r="AQ35">
-        <v>1.58</v>
-      </c>
-      <c r="AR35">
-        <v>1.94</v>
-      </c>
-      <c r="AS35">
-        <v>2.43</v>
-      </c>
-      <c r="AT35">
-        <v>3.15</v>
-      </c>
-      <c r="AU35">
-        <v>2.9</v>
-      </c>
-      <c r="AV35">
-        <v>2.2</v>
-      </c>
-      <c r="AW35">
-        <v>1.76</v>
-      </c>
-      <c r="AX35">
-        <v>1.48</v>
-      </c>
-      <c r="AY35">
-        <v>1.3</v>
-      </c>
-      <c r="AZ35">
-        <v>0</v>
-      </c>
-      <c r="BA35">
-        <v>0</v>
-      </c>
-      <c r="BB35">
-        <v>4</v>
-      </c>
-      <c r="BC35">
-        <v>1.36</v>
-      </c>
-      <c r="BD35" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL35" s="3">
         <v>45783.79166666666</v>
       </c>
     </row>
-    <row r="36" spans="1:56">
+    <row r="36" spans="1:38">
       <c r="A36" s="2">
         <v>45783</v>
       </c>
       <c r="B36" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36" t="s">
         <v>73</v>
       </c>
-      <c r="C36" t="s">
-        <v>89</v>
-      </c>
-      <c r="D36" t="s">
-        <v>91</v>
-      </c>
       <c r="E36" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="F36" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="G36">
         <v>0</v>
       </c>
       <c r="H36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -7028,67 +5084,67 @@
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L36">
-        <v>3.07</v>
+        <v>3.17</v>
       </c>
       <c r="M36">
-        <v>3.02</v>
+        <v>2.92</v>
       </c>
       <c r="N36">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="O36">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="P36">
-        <v>6.75</v>
+        <v>6.25</v>
       </c>
       <c r="Q36">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="R36">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S36">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T36">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U36">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V36">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X36">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y36">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Z36">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AA36">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AB36">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="AC36">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AD36">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AE36">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF36">
         <v>2</v>
@@ -7097,93 +5153,39 @@
         <v>1.75</v>
       </c>
       <c r="AH36">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AI36">
         <v>1.05</v>
       </c>
       <c r="AJ36" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="AK36" t="s">
-        <v>219</v>
-      </c>
-      <c r="AL36">
-        <v>1.58</v>
-      </c>
-      <c r="AM36">
-        <v>1.34</v>
-      </c>
-      <c r="AN36">
-        <v>1.34</v>
-      </c>
-      <c r="AO36">
-        <v>-1</v>
-      </c>
-      <c r="AP36">
-        <v>1.29</v>
-      </c>
-      <c r="AQ36">
-        <v>1.5</v>
-      </c>
-      <c r="AR36">
-        <v>1.81</v>
-      </c>
-      <c r="AS36">
-        <v>2.3</v>
-      </c>
-      <c r="AT36">
-        <v>2.95</v>
-      </c>
-      <c r="AU36">
-        <v>3.2</v>
-      </c>
-      <c r="AV36">
-        <v>2.38</v>
-      </c>
-      <c r="AW36">
-        <v>1.88</v>
-      </c>
-      <c r="AX36">
-        <v>1.54</v>
-      </c>
-      <c r="AY36">
-        <v>1.34</v>
-      </c>
-      <c r="AZ36">
-        <v>0</v>
-      </c>
-      <c r="BA36">
-        <v>0</v>
-      </c>
-      <c r="BB36">
-        <v>2.4</v>
-      </c>
-      <c r="BC36">
-        <v>1.73</v>
-      </c>
-      <c r="BD36" s="3">
+        <v>201</v>
+      </c>
+      <c r="AL36" s="3">
         <v>45783.79166666666</v>
       </c>
     </row>
-    <row r="37" spans="1:56">
+    <row r="37" spans="1:38">
       <c r="A37" s="2">
         <v>45783</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C37" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D37" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E37" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="F37" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -7198,7 +5200,7 @@
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L37">
         <v>2.16</v>
@@ -7273,87 +5275,33 @@
         <v>1</v>
       </c>
       <c r="AJ37" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="AK37" t="s">
-        <v>220</v>
-      </c>
-      <c r="AL37">
-        <v>1.44</v>
-      </c>
-      <c r="AM37">
-        <v>1.34</v>
-      </c>
-      <c r="AN37">
-        <v>1.53</v>
-      </c>
-      <c r="AO37">
-        <v>14</v>
-      </c>
-      <c r="AP37">
-        <v>1.24</v>
-      </c>
-      <c r="AQ37">
-        <v>1.42</v>
-      </c>
-      <c r="AR37">
-        <v>1.77</v>
-      </c>
-      <c r="AS37">
-        <v>2.1</v>
-      </c>
-      <c r="AT37">
-        <v>2.62</v>
-      </c>
-      <c r="AU37">
-        <v>3.6</v>
-      </c>
-      <c r="AV37">
-        <v>2.59</v>
-      </c>
-      <c r="AW37">
-        <v>2.05</v>
-      </c>
-      <c r="AX37">
-        <v>1.67</v>
-      </c>
-      <c r="AY37">
-        <v>1.42</v>
-      </c>
-      <c r="AZ37">
-        <v>0</v>
-      </c>
-      <c r="BA37">
-        <v>0</v>
-      </c>
-      <c r="BB37">
-        <v>1.73</v>
-      </c>
-      <c r="BC37">
-        <v>2.5</v>
-      </c>
-      <c r="BD37" s="3">
+        <v>202</v>
+      </c>
+      <c r="AL37" s="3">
         <v>45783.8125</v>
       </c>
     </row>
-    <row r="38" spans="1:56">
+    <row r="38" spans="1:38">
       <c r="A38" s="2">
         <v>45783</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="C38" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D38" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E38" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="F38" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="G38">
         <v>4</v>
@@ -7368,7 +5316,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L38">
         <v>1.92</v>
@@ -7443,87 +5391,33 @@
         <v>1.06</v>
       </c>
       <c r="AJ38" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="AK38" t="s">
-        <v>174</v>
-      </c>
-      <c r="AL38">
-        <v>1.25</v>
-      </c>
-      <c r="AM38">
-        <v>1.33</v>
-      </c>
-      <c r="AN38">
-        <v>1.75</v>
-      </c>
-      <c r="AO38">
-        <v>13</v>
-      </c>
-      <c r="AP38">
-        <v>1.28</v>
-      </c>
-      <c r="AQ38">
-        <v>1.49</v>
-      </c>
-      <c r="AR38">
-        <v>1.79</v>
-      </c>
-      <c r="AS38">
-        <v>2.23</v>
-      </c>
-      <c r="AT38">
-        <v>2.9</v>
-      </c>
-      <c r="AU38">
-        <v>3.2</v>
-      </c>
-      <c r="AV38">
-        <v>2.4</v>
-      </c>
-      <c r="AW38">
-        <v>1.9</v>
-      </c>
-      <c r="AX38">
-        <v>1.56</v>
-      </c>
-      <c r="AY38">
-        <v>1.35</v>
-      </c>
-      <c r="AZ38">
-        <v>0</v>
-      </c>
-      <c r="BA38">
-        <v>0</v>
-      </c>
-      <c r="BB38">
-        <v>1.72</v>
-      </c>
-      <c r="BC38">
-        <v>2.55</v>
-      </c>
-      <c r="BD38" s="3">
+        <v>156</v>
+      </c>
+      <c r="AL38" s="3">
         <v>45783.89583333334</v>
       </c>
     </row>
-    <row r="39" spans="1:56">
+    <row r="39" spans="1:38">
       <c r="A39" s="2">
         <v>45783</v>
       </c>
       <c r="B39" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="C39" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D39" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E39" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="F39" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -7538,7 +5432,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L39">
         <v>2.28</v>
@@ -7613,87 +5507,33 @@
         <v>1.03</v>
       </c>
       <c r="AJ39" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="AK39" t="s">
-        <v>176</v>
-      </c>
-      <c r="AL39">
-        <v>1.4</v>
-      </c>
-      <c r="AM39">
-        <v>1.38</v>
-      </c>
-      <c r="AN39">
-        <v>1.62</v>
-      </c>
-      <c r="AO39">
-        <v>7</v>
-      </c>
-      <c r="AP39">
-        <v>1.23</v>
-      </c>
-      <c r="AQ39">
-        <v>1.42</v>
-      </c>
-      <c r="AR39">
-        <v>1.84</v>
-      </c>
-      <c r="AS39">
-        <v>2.1</v>
-      </c>
-      <c r="AT39">
-        <v>2.62</v>
-      </c>
-      <c r="AU39">
-        <v>3.6</v>
-      </c>
-      <c r="AV39">
-        <v>2.7</v>
-      </c>
-      <c r="AW39">
-        <v>2.1</v>
-      </c>
-      <c r="AX39">
-        <v>1.85</v>
-      </c>
-      <c r="AY39">
-        <v>1.42</v>
-      </c>
-      <c r="AZ39">
-        <v>0</v>
-      </c>
-      <c r="BA39">
-        <v>0</v>
-      </c>
-      <c r="BB39">
-        <v>1.8</v>
-      </c>
-      <c r="BC39">
-        <v>2.5</v>
-      </c>
-      <c r="BD39" s="3">
+        <v>161</v>
+      </c>
+      <c r="AL39" s="3">
         <v>45783.89583333334</v>
       </c>
     </row>
-    <row r="40" spans="1:56">
+    <row r="40" spans="1:38">
       <c r="A40" s="2">
         <v>45783</v>
       </c>
       <c r="B40" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C40" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D40" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E40" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="F40" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -7708,7 +5548,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="L40">
         <v>3.45</v>
@@ -7783,66 +5623,12 @@
         <v>1.1</v>
       </c>
       <c r="AJ40" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="AK40" t="s">
-        <v>221</v>
-      </c>
-      <c r="AL40">
-        <v>1.8</v>
-      </c>
-      <c r="AM40">
-        <v>1.29</v>
-      </c>
-      <c r="AN40">
-        <v>1.26</v>
-      </c>
-      <c r="AO40">
-        <v>7</v>
-      </c>
-      <c r="AP40">
-        <v>1.28</v>
-      </c>
-      <c r="AQ40">
-        <v>1.49</v>
-      </c>
-      <c r="AR40">
-        <v>1.8</v>
-      </c>
-      <c r="AS40">
-        <v>2.23</v>
-      </c>
-      <c r="AT40">
-        <v>2.9</v>
-      </c>
-      <c r="AU40">
-        <v>3.3</v>
-      </c>
-      <c r="AV40">
-        <v>2.4</v>
-      </c>
-      <c r="AW40">
-        <v>1.88</v>
-      </c>
-      <c r="AX40">
-        <v>1.56</v>
-      </c>
-      <c r="AY40">
-        <v>1.35</v>
-      </c>
-      <c r="AZ40">
-        <v>0</v>
-      </c>
-      <c r="BA40">
-        <v>0</v>
-      </c>
-      <c r="BB40">
-        <v>2.63</v>
-      </c>
-      <c r="BC40">
-        <v>1.57</v>
-      </c>
-      <c r="BD40" s="3">
+        <v>203</v>
+      </c>
+      <c r="AL40" s="3">
         <v>45783.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-05-06.xlsx
+++ b/jogos_2025-05-06.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,49 +1056,49 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.58</v>
+        <v>2.23</v>
       </c>
       <c r="M5" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="N5" t="n">
-        <v>2.64</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.5</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.85</v>
+        <v>2.48</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1107,19 +1107,19 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['38', '45']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG5" t="n">
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45783.08333333334</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,34 +1185,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.98</v>
+        <v>2.58</v>
       </c>
       <c r="M6" t="n">
-        <v>3.11</v>
+        <v>2.84</v>
       </c>
       <c r="N6" t="n">
-        <v>3.39</v>
+        <v>2.64</v>
       </c>
       <c r="O6" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1236,32 +1236,32 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['38', '45']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
         <v>1.95</v>
       </c>
-      <c r="AD6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['53']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ6" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45783.08333333334</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,16 +1288,16 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,49 +1314,49 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.03</v>
+        <v>2.26</v>
       </c>
       <c r="M7" t="n">
-        <v>3.21</v>
+        <v>2.98</v>
       </c>
       <c r="N7" t="n">
-        <v>3.18</v>
+        <v>2.93</v>
       </c>
       <c r="O7" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
         <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S7" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.96</v>
+        <v>2.48</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1365,32 +1365,32 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
         <v>1.83</v>
       </c>
-      <c r="AD7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>['88']</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>['90+3']</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45783.08333333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,16 +1417,16 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -1435,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,49 +1443,49 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.26</v>
+        <v>2.03</v>
       </c>
       <c r="M8" t="n">
-        <v>2.98</v>
+        <v>3.21</v>
       </c>
       <c r="N8" t="n">
-        <v>2.93</v>
+        <v>3.18</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
         <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="T8" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.48</v>
+        <v>1.96</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1494,32 +1494,32 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AD8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
         <v>1.67</v>
       </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>['43']</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AJ8" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45783.08333333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,22 +1546,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1572,22 +1572,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="M9" t="n">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>3.39</v>
       </c>
       <c r="O9" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R9" t="n">
         <v>1.44</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1623,19 +1623,19 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AD9" t="n">
         <v>1.8</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['25', '69', '90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AG9" t="n">
@@ -1645,10 +1645,10 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45783.08333333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,49 +1701,49 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="M10" t="n">
-        <v>2.87</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O10" t="n">
         <v>3.1</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.2</v>
-      </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.48</v>
+        <v>1.83</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1752,19 +1752,19 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD10" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD10" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['77', '81']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1', '20', '25', '70']</t>
         </is>
       </c>
       <c r="AG10" t="n">
@@ -1774,10 +1774,10 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45783.08333333334</v>
@@ -1804,60 +1804,60 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q11" t="n">
         <v>4</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T11" t="n">
         <v>3.25</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1881,19 +1881,19 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['77', '81']</t>
+          <t>['25', '69', '90+4']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['1', '20', '25', '70']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG11" t="n">
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45783.08333333334</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Roasso Kumamoto</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,22 +1959,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.37</v>
+        <v>2.93</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N12" t="n">
-        <v>2.57</v>
+        <v>2.22</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="P12" t="n">
         <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
         <v>1.5</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="AG12" t="n">
@@ -2032,10 +2032,10 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45783.125</v>
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Roasso Kumamoto</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,34 +2088,34 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="M13" t="n">
-        <v>3.05</v>
+        <v>3.39</v>
       </c>
       <c r="N13" t="n">
-        <v>2.22</v>
+        <v>2.01</v>
       </c>
       <c r="O13" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="T13" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2139,19 +2139,19 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['36']</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AG13" t="n">
@@ -2161,10 +2161,10 @@
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45783.125</v>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,34 +2217,34 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.05</v>
+        <v>2.37</v>
       </c>
       <c r="M14" t="n">
-        <v>3.39</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>2.01</v>
+        <v>2.57</v>
       </c>
       <c r="O14" t="n">
+        <v>3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q14" t="n">
         <v>4</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.75</v>
-      </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2268,19 +2268,19 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['27']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>['48']</t>
         </is>
       </c>
       <c r="AG14" t="n">
@@ -2290,10 +2290,10 @@
         <v>0</v>
       </c>
       <c r="AI14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>2.4</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.67</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45783.125</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shimizu S-Pulse</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,49 +2475,49 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="M16" t="n">
-        <v>3.04</v>
+        <v>3.27</v>
       </c>
       <c r="N16" t="n">
-        <v>3.39</v>
+        <v>2.81</v>
       </c>
       <c r="O16" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.44</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.33</v>
-      </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2526,19 +2526,19 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '53']</t>
         </is>
       </c>
       <c r="AG16" t="n">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45783.16666666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,49 +2604,49 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="M17" t="n">
-        <v>3.27</v>
+        <v>3.04</v>
       </c>
       <c r="N17" t="n">
-        <v>2.81</v>
+        <v>3.39</v>
       </c>
       <c r="O17" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="T17" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2655,32 +2655,32 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['23']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['5', '53']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45783.16666666666</v>
@@ -3729,29 +3729,29 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="N26" t="n">
-        <v>2.07</v>
+        <v>2.31</v>
       </c>
       <c r="O26" t="n">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="P26" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="S26" t="n">
-        <v>2.85</v>
+        <v>2.46</v>
       </c>
       <c r="T26" t="n">
-        <v>2.55</v>
+        <v>3.35</v>
       </c>
       <c r="U26" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="X26" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3828,20 +3828,20 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['85', '88']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.29</v>
       </c>
       <c r="AI26" t="n">
         <v>2.3</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45783.5</v>
@@ -3858,29 +3858,29 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="M27" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.31</v>
+        <v>2.07</v>
       </c>
       <c r="O27" t="n">
-        <v>3.66</v>
+        <v>3.8</v>
       </c>
       <c r="P27" t="n">
-        <v>1.92</v>
+        <v>2.09</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="R27" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>2.46</v>
+        <v>2.85</v>
       </c>
       <c r="T27" t="n">
-        <v>3.35</v>
+        <v>2.55</v>
       </c>
       <c r="U27" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="V27" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="X27" t="n">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3957,20 +3957,20 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85', '88']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AI27" t="n">
         <v>2.3</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45783.5</v>
@@ -4374,35 +4374,35 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="M31" t="n">
-        <v>2.7</v>
+        <v>3.31</v>
       </c>
       <c r="N31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S31" t="n">
         <v>3</v>
       </c>
-      <c r="O31" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="T31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
         <v>1.7</v>
       </c>
-      <c r="Q31" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AD31" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36', '61']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31', '45+2']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45783.58333333334</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.09</v>
+        <v>2.5</v>
       </c>
       <c r="M32" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="N32" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="O32" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="P32" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="Q32" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ32" t="n">
         <v>2.75</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>['74']</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>['6']</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.67</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45783.58333333334</v>
@@ -4632,119 +4632,119 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45783.58333333334</v>
@@ -5029,16 +5029,16 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Alianza Lima</t>
+          <t>Carabobo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
         <v>2</v>
@@ -5055,49 +5055,49 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.17</v>
+        <v>5.7</v>
       </c>
       <c r="M36" t="n">
-        <v>2.92</v>
+        <v>3.73</v>
       </c>
       <c r="N36" t="n">
-        <v>2.17</v>
+        <v>1.48</v>
       </c>
       <c r="O36" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P36" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="R36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z36" t="n">
         <v>1.53</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.48</v>
       </c>
       <c r="AA36" t="n">
         <v>4.75</v>
@@ -5106,32 +5106,32 @@
         <v>1.18</v>
       </c>
       <c r="AC36" t="n">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>['35', '89']</t>
+          <t>['22', '90+1']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.53</v>
+        <v>2.37</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AI36" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45783.79166666666</v>
@@ -5158,16 +5158,16 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Carabobo</t>
+          <t>Alianza Lima</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>2</v>
@@ -5184,49 +5184,49 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>5.7</v>
+        <v>3.17</v>
       </c>
       <c r="M37" t="n">
-        <v>3.73</v>
+        <v>2.92</v>
       </c>
       <c r="N37" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="O37" t="n">
+        <v>4</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z37" t="n">
         <v>1.48</v>
-      </c>
-      <c r="O37" t="n">
-        <v>8</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.53</v>
       </c>
       <c r="AA37" t="n">
         <v>4.75</v>
@@ -5235,32 +5235,32 @@
         <v>1.18</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>['22', '90+1']</t>
+          <t>['35', '89']</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>2.37</v>
+        <v>1.53</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="AI37" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45783.79166666666</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,22 +5545,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.28</v>
+        <v>1.92</v>
       </c>
       <c r="M40" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="N40" t="n">
-        <v>3.61</v>
+        <v>3.69</v>
       </c>
       <c r="O40" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="R40" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="S40" t="n">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="T40" t="n">
         <v>3.2</v>
       </c>
       <c r="U40" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="V40" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W40" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="X40" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AA40" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AC40" t="n">
         <v>2</v>
       </c>
       <c r="AD40" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>['25', '30', '39', '85']</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH40" t="n">
         <v>1.75</v>
       </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>['90+3']</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AI40" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45783.89583333334</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,22 +5674,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="M41" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="N41" t="n">
-        <v>3.69</v>
+        <v>3.61</v>
       </c>
       <c r="O41" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="P41" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="R41" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="S41" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="T41" t="n">
         <v>3.2</v>
       </c>
       <c r="U41" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="V41" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W41" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X41" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AA41" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AC41" t="n">
         <v>2</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>['25', '30', '39', '85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45783.89583333334</v>
